--- a/20260804_権限設定_00_定義表.xlsx
+++ b/20260804_権限設定_00_定義表.xlsx
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>設計意図（なぜそう作るか）は仕様書にある。受入条件表はそれを「この数値を満たせば実装完了」に翻訳する場であり、意図を新しく作る場ではない。1対1で対応する必要はなく、1つの意図が複数の条件に、1つの条件が複数の検証ケースに展開される。</t>
+          <t>2と3は独立して使える。受入条件表は合格ラインと確認する画面だけで判定でき、検証プランは操作と期待値だけで実施できる。相互参照は辿るためのリンクであって依存ではない。1対1で対応する必要もなく、1条件が複数ケースに、1ケースが複数条件に展開される。</t>
         </is>
       </c>
     </row>

--- a/20260804_権限設定_00_定義表.xlsx
+++ b/20260804_権限設定_00_定義表.xlsx
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2と3は独立して使える。受入条件表は合格ラインと確認する画面だけで判定でき、検証プランは操作と期待値だけで実施できる。相互参照は辿るためのリンクであって依存ではない。1対1で対応する必要もなく、1条件が複数ケースに、1ケースが複数条件に展開される。</t>
+          <t>2と3は独立して使える。受入条件表は合格ラインと確認する画面だけで判定でき、検証プランは操作と期待値だけで実施できる。相互参照は辿るためのリンクであって依存ではない。</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>AC-23 ／ AC-24 ／ AC-25 ／ AC-26 ／ AC-32</t>
+          <t>AC-23 ／ AC-24 ／ AC-25 ／ AC-26 ／ AC-32 ／ AC-34</t>
         </is>
       </c>
     </row>
